--- a/data/daily/2026-09/2026-09-06.xlsx
+++ b/data/daily/2026-09/2026-09-06.xlsx
@@ -1170,14 +1170,89 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1267,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,135 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1425,52 +1425,177 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,154 +1603,29 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -3081,7 +3081,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3089,34 +3089,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3124,27 +3124,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
         </is>
       </c>
     </row>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
+          <t>45,000원</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>45,000원</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>종근당건강 관절연골엔 MSM 60정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4077,19 +4077,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581121&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/e7PvuolyW0jdoQAtpzxC591581121_00_01e7PvuolyW0jdoQAtpzxC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,34 +4097,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4142,17 +4142,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4182,19 +4182,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4287,19 +4287,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,34 +4307,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
+          <t>동국제약 마데카 저분자 콜라겐C</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4357,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581111&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910603&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/ryqqbn8htR0Ir3fAZcjp591581111_00_01ryqqbn8htR0Ir3fAZcjp.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250530/iFPtDwREEwh2EwWoojJJ610910603_00_01iFPtDwREEwh2EwWoojJJ.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 4050 에너지 올인원 12포 12일분</t>
+          <t>유한양행 운동부스터 생유산균 스틱 5포 5일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991014&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651655&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/nEaU2dcD2F8jaTQXSIb5033991014_00_00nEaU2dcD2F8jaTQXSIb5.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/CxT93DcA0d824G3UBlAN600651655_00_00CxT93DcA0d824G3UBlAN.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,17 +4512,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4569,52 +4569,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>종근당건강</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>유한양행</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>판티오</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 관절연골엔 MSM 60정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 락토핏 골드</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
+          <t>동국제약 마데카 저분자 콜라겐C</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 4050 에너지 올인원 12포 12일분</t>
+          <t>유한양행 운동부스터 생유산균 스틱 5포 5일분</t>
         </is>
       </c>
     </row>
@@ -4688,37 +4688,37 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4885,24 +4885,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,27 +4910,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>닥터파이토 루테인 지아잔틴 아스타잔틴 30캡슐 (1개월분)</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>닥터파이토</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14,360원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245935&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024593503ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259818&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025981802ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355449ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,27 +4980,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>90,000원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549609ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>24,200원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733452ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18,400원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29,800원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020888832ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[산리오캐릭터즈에디션/9월올영픽] 비비랩 석류콜라겐S 14포 기획 (+6포) (+마이멜로디 마켓백)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>19,200원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000226014&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022601428ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>115,000원</t>
+          <t>18,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000207974&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020797409ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>8APM 식물성 멜라토닌 함유 멜라피스 800mg 20정 (20일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>8APM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244289&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024428908ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -5350,27 +5350,27 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5387,47 +5387,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>닥터파이토</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>닥터아돌</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>비비랩</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>비비랩</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>8APM</t>
         </is>
       </c>
     </row>
@@ -5439,52 +5439,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>닥터파이토 루테인 지아잔틴 아스타잔틴 30캡슐 (1개월분)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[산리오캐릭터즈에디션/9월올영픽] 비비랩 석류콜라겐S 14포 기획 (+6포) (+마이멜로디 마켓백)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>8APM 식물성 멜라토닌 함유 멜라피스 800mg 20정 (20일분)</t>
         </is>
       </c>
     </row>
@@ -5496,52 +5496,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>10,900원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>14,360원</t>
-        </is>
-      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>90,000원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>24,200원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>26,900원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>55,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>19,200원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>18,400원</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>29,800원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>115,000원</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5667,7 +5667,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5677,19 +5677,19 @@
         <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5699,10 +5699,10 @@
         <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5711,20 +5711,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>8</v>
       </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -5733,7 +5733,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5743,10 +5743,10 @@
         <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -5755,20 +5755,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -5777,7 +5777,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5787,32 +5787,32 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5834,16 +5834,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5853,12 +5853,34 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
